--- a/config/battle_config.xlsx
+++ b/config/battle_config.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -607,6 +607,177 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>第一夜 · 参道灯笼影（教学战）</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>第一章棺女·夜一：仅扑击/尖啸，认识灵墨与出牌</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>res://assets/bg/corridor_battle_test.png</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{"start": 3, "per_turn": 1, "phase2_from_turn": 3, "phase2_bonus": 2, "tier_attack_mult": {"weak": 0.7, "normal": 1.0, "empowered": 1.3, "berserk": 1.5}, "weak_below": 3, "empowered_from": 6, "berserk_from": 8}</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>{"min_seal_points": 2, "min_spirit": 6}</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{"name": "凛音", "sprite": "res://assets/chars/rinne_idle.png", "hp": 30, "height_px": 450, "pos": [210, 930], "anims": {"idle": ["res://assets/chars/anims/rinne_idle_f1.png", "res://assets/chars/anims/rinne_idle_f2.png", "res://assets/chars/anims/rinne_idle_f3.png", "res://assets/chars/anims/rinne_idle_f4.png"], "walk": ["res://assets/chars/anims/rinne_walk_f1.png", "res://assets/chars/anims/rinne_walk_f2.png", "res://assets/chars/anims/rinne_walk_f3.png", "res://assets/chars/anims/rinne_walk_f4.png", "res://assets/chars/anims/rinne_walk_f5.png", "res://assets/chars/anims/rinne_walk_f6.png"], "cast": ["res://assets/chars/anims/rinne_cast_f1.png", "res://assets/chars/anims/rinne_cast_f2.png", "res://assets/chars/anims/rinne_cast_f3.png", "res://assets/chars/anims/rinne_cast_f4.png", "res://assets/chars/anims/rinne_cast_f5.png"], "fps": 10}}</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>{"copies": 2, "hand_limit": 5, "comment": "牌组循环：每张卡 copies 份入抽牌堆，回合补牌至 hand_limit，弃牌堆耗尽重洗"}</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>教学战：纸人形只会扑击与尖啸。引导：攻击牌打立绘 / 引燃场景槽 / 鸣钟震慑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>第三夜 · 回廊深处·抬棺</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>第一章棺女·夜三：抬棺队列两波，封印教学</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>res://assets/bg/corridor_battle_test.png</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{"start": 5, "per_turn": 1, "phase2_from_turn": 3, "phase2_bonus": 2, "tier_attack_mult": {"weak": 0.7, "normal": 1.0, "empowered": 1.3, "berserk": 1.5}, "weak_below": 3, "empowered_from": 6, "berserk_from": 8}</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>{"min_seal_points": 2, "min_spirit": 6}</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{"name": "凛音", "sprite": "res://assets/chars/rinne_idle.png", "hp": 30, "height_px": 450, "pos": [210, 930], "anims": {"idle": ["res://assets/chars/anims/rinne_idle_f1.png", "res://assets/chars/anims/rinne_idle_f2.png", "res://assets/chars/anims/rinne_idle_f3.png", "res://assets/chars/anims/rinne_idle_f4.png"], "walk": ["res://assets/chars/anims/rinne_walk_f1.png", "res://assets/chars/anims/rinne_walk_f2.png", "res://assets/chars/anims/rinne_walk_f3.png", "res://assets/chars/anims/rinne_walk_f4.png", "res://assets/chars/anims/rinne_walk_f5.png", "res://assets/chars/anims/rinne_walk_f6.png"], "cast": ["res://assets/chars/anims/rinne_cast_f1.png", "res://assets/chars/anims/rinne_cast_f2.png", "res://assets/chars/anims/rinne_cast_f3.png", "res://assets/chars/anims/rinne_cast_f4.png", "res://assets/chars/anims/rinne_cast_f5.png"], "fps": 10}}</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{"copies": 2, "hand_limit": 5, "comment": "牌组循环：每张卡 copies 份入抽牌堆，回合补牌至 hand_limit，弃牌堆耗尽重洗"}</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>两波压制：抬棺纸人会猛扑（重击）。灵气≥6 且阵眼≥2 时贴符可封印斩杀。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>第四夜 · 本殿黄昏·棺中镜</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>第一章棺女·夜四：残响群 + 执棺精英（护体/执念）</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>res://assets/bg/honden_battle.png</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{"start": 6, "per_turn": 1, "phase2_from_turn": 3, "phase2_bonus": 2, "tier_attack_mult": {"weak": 0.7, "normal": 1.0, "empowered": 1.3, "berserk": 1.5}, "weak_below": 3, "empowered_from": 6, "berserk_from": 8}</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>{"min_seal_points": 2, "min_spirit": 6}</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{"name": "凛音", "sprite": "res://assets/chars/rinne_idle.png", "hp": 30, "height_px": 450, "pos": [210, 930], "anims": {"idle": ["res://assets/chars/anims/rinne_idle_f1.png", "res://assets/chars/anims/rinne_idle_f2.png", "res://assets/chars/anims/rinne_idle_f3.png", "res://assets/chars/anims/rinne_idle_f4.png"], "walk": ["res://assets/chars/anims/rinne_walk_f1.png", "res://assets/chars/anims/rinne_walk_f2.png", "res://assets/chars/anims/rinne_walk_f3.png", "res://assets/chars/anims/rinne_walk_f4.png", "res://assets/chars/anims/rinne_walk_f5.png", "res://assets/chars/anims/rinne_walk_f6.png"], "cast": ["res://assets/chars/anims/rinne_cast_f1.png", "res://assets/chars/anims/rinne_cast_f2.png", "res://assets/chars/anims/rinne_cast_f3.png", "res://assets/chars/anims/rinne_cast_f4.png", "res://assets/chars/anims/rinne_cast_f5.png"], "fps": 10}}</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{"copies": 2, "hand_limit": 5}</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>精英带棺气护体（需先破阵）与执念槽（对应槽位被激活时暴怒）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -618,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1100,6 +1271,418 @@
         <v>3</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>纸人形</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>res://assets/chars/enemy_paper_doll.png</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>[1400, 800]</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>["attack", "attack", "howl"]</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>{"attack": "扑击", "howl": "尖啸 —— 灵气上升！"}</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>{"idle": ["res://assets/chars/anims/paperdoll_idle_f1.png", "res://assets/chars/anims/paperdoll_idle_f2.png", "res://assets/chars/anims/paperdoll_idle_f3.png", "res://assets/chars/anims/paperdoll_idle_f4.png"], "fps": 5}</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>纸人形·抬棺</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>res://assets/chars/enemy_paper_doll.png</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>[1400, 800]</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>["attack", "pounce", "attack", "howl"]</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>{"attack": "扑击", "pounce": "猛扑（重击）", "howl": "尖啸 —— 灵气上升！"}</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>{"idle": ["res://assets/chars/anims/paperdoll_idle_f1.png", "res://assets/chars/anims/paperdoll_idle_f2.png", "res://assets/chars/anims/paperdoll_idle_f3.png", "res://assets/chars/anims/paperdoll_idle_f4.png"], "fps": 5}</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>纸人形·残响</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>第二波：独立立绘（日式批次生成，紫怨纸人），波次轮换登场验证</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>res://assets/chars/enemy_paper_doll_echo.png</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>[1400, 800]</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>["pounce", "attack", "attack"]</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>{"attack": "扑击", "pounce": "猛扑（重击）"}</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>纸人形·残响</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>第二波：独立立绘（日式批次生成，紫怨纸人），波次轮换登场验证</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>res://assets/chars/enemy_paper_doll_echo.png</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[1400, 800]</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>["pounce", "attack", "howl", "attack"]</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>{"attack": "扑击", "pounce": "猛扑（重击）", "howl": "尖啸 —— 灵气上升！"}</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>纸人形·执棺</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>res://assets/chars/enemy_paper_doll.png</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>slot_shoji</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>执念：守棺 —— 仪式未成，棺不可开</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>[1400, 800]</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>["attack", "attack", "pounce", "howl"]</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>{"attack": "扑击", "pounce": "猛扑（重击）", "howl": "尖啸 —— 灵气上升！"}</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>{"idle": ["res://assets/chars/anims/paperdoll_idle_f1.png", "res://assets/chars/anims/paperdoll_idle_f2.png", "res://assets/chars/anims/paperdoll_idle_f3.png", "res://assets/chars/anims/paperdoll_idle_f4.png"], "fps": 5}</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1111,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1540,6 +2123,558 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>slot_shoji</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>纸门</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[0.13, 0.38]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>["slot_rope"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>slot_rope</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>注连绳</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>[0.38, 0.22]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>["slot_shoji", "slot_bell"]</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>slot_bell</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>吊钟</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[0.53, 0.3]</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>["slot_rope", "slot_basin"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>slot_basin</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>水钵</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[0.68, 0.55]</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>["slot_bell", "slot_eaves"]</t>
+        </is>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>slot_eaves</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>檐角</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>[0.87, 0.32]</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>["slot_basin"]</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>slot_shoji</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>纸门</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[0.13, 0.38]</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>["slot_rope"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>slot_rope</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>注连绳</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[0.38, 0.22]</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>["slot_shoji", "slot_bell"]</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>slot_bell</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>吊钟</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[0.53, 0.3]</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>["slot_rope", "slot_basin"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>slot_basin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>水钵</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[0.68, 0.55]</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>["slot_bell", "slot_eaves"]</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>slot_eaves</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>檐角</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>[0.87, 0.32]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>["slot_basin"]</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>slot_shoji</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>纸门</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[0.13, 0.38]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>["slot_rope"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>slot_rope</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>注连绳</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.38, 0.22]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>["slot_shoji", "slot_bell"]</t>
+        </is>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>slot_bell</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>吊钟</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.53, 0.3]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>["slot_rope", "slot_basin"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>slot_basin</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>水钵</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[0.68, 0.55]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>["slot_bell", "slot_eaves"]</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>slot_eaves</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>檐角</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>[0.87, 0.32]</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>["slot_basin"]</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1551,7 +2686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3143,6 +4278,1957 @@
         </is>
       </c>
       <c r="P28" t="inlineStr">
+        <is>
+          <t>回旋短刃回锋过隙，造成 5 点伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>居合斩</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>["weapon"]</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_slash.png</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>挥刀斩击敌方立绘，造成等同于牌面的伤害。燃烧的敌人受到恐惧侵蚀。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ignite</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>引燃</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>burning</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>homura</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>["fire"]</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_ignite.png</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>点燃目标场景槽。火势每回合沿相连槽位蔓延，灼烧其中的敌人并令其恐惧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>bell</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>鸣钟</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ringing</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>["bell","sound"]</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_bell.png</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>摇响吊钟：敌人下回合眩晕无法行动；鸣响也会惊起连锁，清除场景上的燃烧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>结界符</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>sealed</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_seal.png</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>将结界符贴在阵眼上。集齐 2 处阵眼且灵气≥6 时，封印敌人，直接退治。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>seal2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>结界符·贰</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>sealed</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_seal.png</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>将结界符贴在阵眼上。集齐 2 处阵眼且灵气≥6 时，封印敌人，直接退治。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>guard</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>守势</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>{"shield": 4}</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_defense_stance.png</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>获得 4 点护盾。护盾先于生命承伤，到你下次回合开始清空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>amulet</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>护身符</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>{"shield": 7, "cleanse": 1}</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_paper_amulet.png</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>获得 7 点护盾，并净化一个可净化的负面状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ch1_night1</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>expose</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>识破</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>{"mark": 1}</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>["sight"]</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_seeing_eye.png</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>对一名敌人附加 1 层标记。标记最多 3 层，留存至本场战斗结束，只被明确消耗它的牌消耗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>居合斩</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>8</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>["weapon"]</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_slash.png</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>挥刀斩击敌方立绘，造成等同于牌面的伤害。燃烧的敌人受到恐惧侵蚀。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ignite</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>引燃</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>burning</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>homura</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>["fire"]</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_ignite.png</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>点燃目标场景槽。火势每回合沿相连槽位蔓延，灼烧其中的敌人并令其恐惧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bell</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>鸣钟</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ringing</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>["bell","sound"]</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_bell.png</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>摇响吊钟：敌人下回合眩晕无法行动；鸣响也会惊起连锁，清除场景上的燃烧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>结界符</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>sealed</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_seal.png</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>将结界符贴在阵眼上。集齐 2 处阵眼且灵气≥6 时，封印敌人，直接退治。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>seal2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>结界符·贰</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>sealed</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_seal.png</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>将结界符贴在阵眼上。集齐 2 处阵眼且灵气≥6 时，封印敌人，直接退治。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>guard</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>守势</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>{"shield": 4}</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_defense_stance.png</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>获得 4 点护盾。护盾先于生命承伤，到你下次回合开始清空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>amulet</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>护身符</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>{"shield": 7, "cleanse": 1}</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_paper_amulet.png</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>获得 7 点护盾，并净化一个可净化的负面状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>expose</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>识破</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>{"mark": 1}</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>["sight"]</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_seeing_eye.png</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>对一名敌人附加 1 层标记。标记最多 3 层，留存至本场战斗结束，只被明确消耗它的牌消耗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>chase_slash</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>追符斩</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>6</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>{"consume_mark": 1, "bonus": 5}</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>["weapon", "talisman"]</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_slash.png</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>造成 6 点伤害；消耗目标 1 层标记时，额外造成 5 点伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>breath</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>净息</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>{"spirit": -2}</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>["breath"]</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_bell.png</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>灵气降低 2。可能避开灵压高压，也可能推迟封印时机。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>flame_slash</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>流火斩</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>7</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>homura</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>["weapon","fire"]</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_flame_katana.png</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>焰华一脉的燃火斩击，造成 7 点伤害。场上有燃烧槽位时，攻击照旧获得火助。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>twin_swallow</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>双燕斩</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>12</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>["weapon"]</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_twin_arc.png</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>双弧交斩的全力一击，造成 12 点伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>12</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>stack_sigil</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>叠符</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>{"mark": 2}</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_talisman_stack.png</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>为敌方贴上 2 层标记。标记满层时，将被追符斩类卡牌迸发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>13</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>break_ward</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>破障</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>4</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>{"consume_mark": 1, "bonus": 4}</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>["weapon"]</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_barrier_break.png</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>消耗 1 层标记，使本次伤害 +4；无标记时退为一道普通快斩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>14</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>pure_fire</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>净火</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>{"cleanse": 2, "spirit": -1}</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>["fire"]</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_purify_flame.png</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>净火焚秽：净化 2 层负面效果，并以一缕净火压低全场灵气 1 点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ch1_night3</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gather_ink</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>蓄墨</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>{"draw": 1}</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>["ink"]</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_ink_brush.png</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>不耗灵墨。凝神蓄墨，立即抽 1 张牌。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>居合斩</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>8</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>["weapon"]</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_slash.png</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>挥刀斩击敌方立绘，造成等同于牌面的伤害。燃烧的敌人受到恐惧侵蚀。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ignite</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>引燃</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>burning</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>homura</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>["fire"]</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_ignite.png</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>点燃目标场景槽。火势每回合沿相连槽位蔓延，灼烧其中的敌人并令其恐惧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bell</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>鸣钟</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ringing</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>["bell","sound"]</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_bell.png</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>摇响吊钟：敌人下回合眩晕无法行动；鸣响也会惊起连锁，清除场景上的燃烧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>spill</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>倾覆</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>spilled</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>["water"]</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_spill.png</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>打翻槽位上的水器：扑灭与其相连槽位的火势。水克火——与鸣钟惊焰并列为灭火两环。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>结界符</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>sealed</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_seal.png</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>将结界符贴在阵眼上。集齐 2 处阵眼且灵气≥6 时，封印敌人，直接退治。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>seal2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>结界符·贰</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>sealed</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>["talisman"]</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_val_seal.png</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>将结界符贴在阵眼上。集齐 2 处阵眼且灵气≥6 时，封印敌人，直接退治。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hold_breath</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>屏息</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>{"shield": 2, "draw": 1}</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>["mist"]</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_mist_guard.png</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>屏息凝神：获得 2 点护盾，并抽 1 张牌。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>call_soul</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>唤灵</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>zhongkui</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>{"spirit": 2, "draw": 1}</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>["spirit"]</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_spirit_wisps.png</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>唤亡者残灵助阵：灵气 +2（当心逢魔压力），并抽 1 张牌。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>nail_shadow</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>钉影</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>9</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>rinne</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>{"consume_mark": 2, "bonus": 8}</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>["weapon"]</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_nail_strike.png</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>消耗至多 2 层标记、每层伤害 +8 的终结钉刺。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>9</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>paper_aegis</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>纸盾</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>{"shield": 2}</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>["paper"]</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_paper_shield.png</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>不耗灵墨。折和纸为盾，获得 2 点护盾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ch1_night4</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>10</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>return_edge</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>回锋</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>5</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>homura</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>["weapon"]</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>res://assets/ui/cardart_e_return_blade.png</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>回旋短刃回锋过隙，造成 5 点伤害。</t>
         </is>

--- a/config/battle_config.xlsx
+++ b/config/battle_config.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>res://assets/bg/corridor_battle_test.png</t>
+          <t>res://assets/bg/approach_battle.png</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
